--- a/human_eval/sheet_honnin_pilot.xlsx
+++ b/human_eval/sheet_honnin_pilot.xlsx
@@ -928,7 +928,7 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>P1-3</t>
+          <t>Q22DD5</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>P2-1</t>
+          <t>Q85ACB</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>P1-1</t>
+          <t>QB3345</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>P2-3</t>
+          <t>QC6DCB</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>P1-2</t>
+          <t>Q9D70C</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>P2-2</t>
+          <t>QD9788</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1280,42 +1280,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P1-3</t>
+          <t>Q22DD5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P2-1</t>
+          <t>Q85ACB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P1-1</t>
+          <t>QB3345</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P2-3</t>
+          <t>QC6DCB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P1-2</t>
+          <t>Q9D70C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P2-2</t>
+          <t>QD9788</t>
         </is>
       </c>
     </row>
